--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1864,6 +1864,208 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128621071</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90954</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545508</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7012696</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128621021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92736</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>stugutjärnen, ammerån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>545385</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012832</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 10982-2025 artfynd.xlsx
+++ b/artfynd/A 10982-2025 artfynd.xlsx
@@ -1869,7 +1869,7 @@
         <v>128621071</v>
       </c>
       <c r="B12" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>128621021</v>
       </c>
       <c r="B13" t="n">
-        <v>92805</v>
+        <v>92813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
